--- a/outputs/ozon_facemask_cards/ozon_facemasks_2026-08-06.xlsx
+++ b/outputs/ozon_facemask_cards/ozon_facemasks_2026-08-06.xlsx
@@ -2636,164 +2636,550 @@
       <c r="AZ11" s="4" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Disney</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Набор корейских тканевых масок для лица 10 шт JMSolution</t>
+        </is>
+      </c>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
+      <c r="F12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="I12" s="6" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-      <c r="P12" s="4" t="n"/>
-      <c r="Q12" s="4" t="n"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2039610320817</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>405</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/13.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/14.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/15.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/16.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/17.webp</t>
+        </is>
+      </c>
       <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
-      <c r="T12" s="4" t="n"/>
-      <c r="U12" s="4" t="n"/>
-      <c r="V12" s="4" t="n"/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>JMSolution</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Disney</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
-      <c r="Y12" s="4" t="n"/>
-      <c r="Z12" s="4" t="n"/>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>Water; Methylpropanediol; Glycerin; Glycereth-26; PEG/PPG-17/6 Copolymer; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Hyaluronic Acid; Collagen Extract; Allantoin; Trehalose; Betaine; Ethylhexylglycerin; Xanthan Gum; Hydroxyethylcellulose; Dipropylene Glycol; Butylene Glycol; Disodium Phosphate; Pentylene Glycol; Sodium Phosphate; Disodium EDTA; Glycine; Serine; Glutamic Acid; Aspartic Acid; Leucine; Alanine; Lysine; Proline; Threonine; Valine; 1,2-Hexanediol; PEG-60 Hydrogenated Castor Oil; Rosa Damascena Flower Water; Rosa Damascena Flower Oil; Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AA12" s="4" t="n"/>
       <c r="AB12" s="4" t="n"/>
-      <c r="AC12" s="4" t="n"/>
+      <c r="AC12" s="4" t="inlineStr">
+        <is>
+          <t>GP Club Co., Ltd.</t>
+        </is>
+      </c>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
-      <c r="AF12" s="4" t="n"/>
+      <c r="AF12" s="4" t="inlineStr">
+        <is>
+          <t>Набор тканевых масок для лица JMsolution Mask подходят для быстрого ежедневного ухода за кожей.
+Маска для лица выравнивает тон, устраняет тусклость и следы усталости, придаёт коже естественное сияние и отлично увлажняет. Яркий дизайн упаковки с любимыми персонажами Disney делает набор отличным подарком. Содержит гидролат лимона, витамины C, E и B12, а также бета-глюкан, комплекс аминокислот и пробиотики.</t>
+        </is>
+      </c>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
-      <c r="AI12" s="4" t="n"/>
-      <c r="AJ12" s="4" t="n"/>
-      <c r="AK12" s="4" t="n"/>
-      <c r="AL12" s="4" t="n"/>
-      <c r="AM12" s="4" t="n"/>
-      <c r="AN12" s="4" t="n"/>
-      <c r="AO12" s="4" t="n"/>
+      <c r="AI12" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="inlineStr">
+        <is>
+          <t>Гиалуроновая кислота;Коллаген</t>
+        </is>
+      </c>
+      <c r="AK12" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL12" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM12" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение;Питание</t>
+        </is>
+      </c>
+      <c r="AN12" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO12" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
       <c r="AP12" s="4" t="n"/>
-      <c r="AQ12" s="4" t="n"/>
-      <c r="AR12" s="4" t="n"/>
-      <c r="AS12" s="4" t="n"/>
+      <c r="AQ12" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR12" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS12" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
       <c r="AT12" s="4" t="n"/>
-      <c r="AU12" s="4" t="n"/>
-      <c r="AV12" s="4" t="n"/>
+      <c r="AU12" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV12" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AW12" s="4" t="n"/>
-      <c r="AX12" s="4" t="n"/>
+      <c r="AX12" s="4" t="n">
+        <v>1095</v>
+      </c>
       <c r="AY12" s="4" t="n"/>
       <c r="AZ12" s="4" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Маски для лица тканевые JMSolution</t>
+        </is>
+      </c>
       <c r="D13" s="5" t="n"/>
       <c r="E13" s="5" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="F13" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-      <c r="P13" s="4" t="n"/>
-      <c r="Q13" s="4" t="n"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2039610565850</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="N13" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/13.webp</t>
+        </is>
+      </c>
       <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
-      <c r="T13" s="4" t="n"/>
-      <c r="U13" s="4" t="n"/>
-      <c r="V13" s="4" t="n"/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>JMSolution</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>10</v>
+      </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
-      <c r="Y13" s="4" t="n"/>
-      <c r="Z13" s="4" t="n"/>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycerin; Dipropylene Glycol; Sea Water; Butylene Glycol; 1,2-Hexanediol; Hydrolyzed Collagen; Hydrolyzed Conchiolin Protein; Pearl Extract; Undaria Pinnatifida Extract; Codium Fragile Extract; Enteromorpha Compressa Extract; Laminaria Japonica Extract; Salicornia Herbacea Extract; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Sodium Acetylated Hyaluronate; Olive Oil; Tocopheryl Acetate; Polysorbate 20; Ethylhexylglycerin; Carbomer; Tromethamine; Disodium EDTA; Phenoxyethanol; Fragrance</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AA13" s="4" t="n"/>
       <c r="AB13" s="4" t="n"/>
-      <c r="AC13" s="4" t="n"/>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>GP Club Co., Ltd.</t>
+        </is>
+      </c>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
-      <c r="AF13" s="4" t="n"/>
+      <c r="AF13" s="4" t="inlineStr">
+        <is>
+          <t>Маски для лица тканевые от корейского бренда JMsolution — настоящий экспресс-уход за кожей. Эффективные и универсальные составы, которые подойдут каждой девушке. Благодаря ультратонкой основе, проработанному лекалу и большому количеству эссенции, маска тканевая для лица всего за 20 минут интенсивно насыщает кожу влагой, помогает снять красноту, придавая коже естественное здоровое сияние.Премиальные подарочные наборы масок представлены из 10 шт в боксе. Маски для лица корейские для интенсивного ухода за кожей лица позволит познакомиться с разными масками бренда. Маски выравнивают цвет лица, тон и рельеф кожи, снимает отеки, разглаживает морщины, а также осветляет пигментацию и оказывает лифтинг - эффект. Набор масок тканевых подойдет любому типу кожи: тусклой, нормальной, проблемной, увядающей и антивозрастной. Маска увлажняющая, отбеливающая, восстанавливающая, питающая. Она убирает сухость и шелушение, делает кожу более нежной, гладкой, сияющей. Благодаря ей, кожа становится светлее, очищается и становится более подтянутой. Влажные тканевые маски для лица набор – это и омолаживающий эффект. Успокаивающая маска эффективно борется с проблемами кожи, снимает напряжение и усталость, раздражения и воспаления, устраняет отёки.
+Особым спросом у девушек и женщин пользуются ассорти масок, разных составов в подарочной коробке. Косметические маски в боксе популярны как подарочный набор уходовой косметики.</t>
+        </is>
+      </c>
       <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
-      <c r="AI13" s="4" t="n"/>
-      <c r="AJ13" s="4" t="n"/>
-      <c r="AK13" s="4" t="n"/>
-      <c r="AL13" s="4" t="n"/>
-      <c r="AM13" s="4" t="n"/>
-      <c r="AN13" s="4" t="n"/>
-      <c r="AO13" s="4" t="n"/>
+      <c r="AI13" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="inlineStr">
+        <is>
+          <t>Коллаген;Гиалуроновая кислота</t>
+        </is>
+      </c>
+      <c r="AK13" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL13" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM13" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение</t>
+        </is>
+      </c>
+      <c r="AN13" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO13" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
       <c r="AP13" s="4" t="n"/>
-      <c r="AQ13" s="4" t="n"/>
-      <c r="AR13" s="4" t="n"/>
-      <c r="AS13" s="4" t="n"/>
+      <c r="AQ13" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR13" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS13" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
       <c r="AT13" s="4" t="n"/>
-      <c r="AU13" s="4" t="n"/>
-      <c r="AV13" s="4" t="n"/>
+      <c r="AU13" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV13" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AW13" s="4" t="n"/>
-      <c r="AX13" s="4" t="n"/>
+      <c r="AX13" s="4" t="n">
+        <v>1095</v>
+      </c>
       <c r="AY13" s="4" t="n"/>
       <c r="AZ13" s="4" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - MASK 15</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Увлажняющие тканевые маски для лица Корея 15 штук Jigott</t>
+        </is>
+      </c>
       <c r="D14" s="5" t="n"/>
       <c r="E14" s="5" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="F14" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2041007880460</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>474</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="N14" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O14" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/2.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/3.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/4.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/5.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/6.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/7.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/8.webp</t>
+        </is>
+      </c>
       <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
-      <c r="T14" s="4" t="n"/>
-      <c r="U14" s="4" t="n"/>
-      <c r="V14" s="4" t="n"/>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>Jigott</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - MASK 15</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="n">
+        <v>15</v>
+      </c>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
-      <c r="Y14" s="4" t="n"/>
-      <c r="Z14" s="4" t="n"/>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycerin; Butylene Glycol; Betaine; Carbomer; Triethanolamine; Disodium EDTA; Hydroxyethylcellulose; Polysorbate 20; Sodium Hyaluronate; Tocopheryl Acetate; Allantoin; Panthenol; Portulaca Oleracea Extract; 1,2-Hexanediol; Phenoxyethanol; Fragrance</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
       <c r="AA14" s="4" t="n"/>
       <c r="AB14" s="4" t="n"/>
-      <c r="AC14" s="4" t="n"/>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>Skinine Cosmetic Co., Ltd.</t>
+        </is>
+      </c>
       <c r="AD14" s="4" t="n"/>
       <c r="AE14" s="4" t="n"/>
-      <c r="AF14" s="4" t="n"/>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Набор увлажняющих масок для лица включает 15 разных масочек тканевых от бренда JIGOTT. Маски не повторяются! 
+В набор косметических корейских масок для лица входят JIGOTT:
+1). Pomegranate Real Ampoule Mask - с гранатом;
+2). Placenta Real Ampoule Mask - с плацентой; 
+3). Camellia Real Ampoule Mask - с камелией;
+4). Vitamin Real Ampoule Mask - с цитрусами и витамином C;
+5). Pearl Real Ampoule Mask - жемчужной пудрой;
+6). Red Ginseng Real Ampoule Mask - с красным женьшенем;
+7). Potato Real Ampoule Mask - картофельная против отеков;
+8). Aloe Real Ampoule Mask - успокаивающая с алоэ;
+9). Black Snail Real Ampoule Mask - антивозрастная с муцином улитки;
+10). Caviar Real Ampoule Mask - с икрой;
+11). Cucumber Real Ampoule Mask - охлаждающая с огурцом;
+12). Green Tea Real Ampoule Mask - тонизирующая с зеленым чаем;
+13). Honey Real Ampoule Mask - питательная с медом;
+14). Hyaluronic Acid Real Ampoule Mask - увлажняющая с гиалуроновой кислотой;
+15). Lotus Real Ampoule Mask - успокаивающая с лотосом.
+Попробуйте сразу весь ассортимент JIGOTT и решите все проблмы вашей кожи: в наборе есть осветляющие, увлажняющие, антивозрастные, противовоспалительные и успокаивающие маски на лицо.
+Тканевую косметическую маску Джиготт можно использовать в любое время дня на очищенное лицо. </t>
+        </is>
+      </c>
       <c r="AG14" s="4" t="n"/>
       <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="n"/>
-      <c r="AJ14" s="4" t="n"/>
-      <c r="AK14" s="4" t="n"/>
-      <c r="AL14" s="4" t="n"/>
-      <c r="AM14" s="4" t="n"/>
-      <c r="AN14" s="4" t="n"/>
-      <c r="AO14" s="4" t="n"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="inlineStr">
+        <is>
+          <t>Гиалуроновая кислота</t>
+        </is>
+      </c>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение</t>
+        </is>
+      </c>
+      <c r="AN14" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
       <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="n"/>
-      <c r="AR14" s="4" t="n"/>
-      <c r="AS14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
       <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="n"/>
-      <c r="AV14" s="4" t="n"/>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV14" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n"/>
+      <c r="AX14" s="4" t="n">
+        <v>1095</v>
+      </c>
       <c r="AY14" s="4" t="n"/>
       <c r="AZ14" s="4" t="n"/>
     </row>

--- a/outputs/ozon_facemask_cards/ozon_facemasks_2026-08-06.xlsx
+++ b/outputs/ozon_facemask_cards/ozon_facemasks_2026-08-06.xlsx
@@ -2641,12 +2641,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>PETITFEE - MASK 5</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Набор корейских тканевых масок для лица 10 шт JMSolution</t>
+          <t>Гидрогелевые маски для лица набор 5 шт. Petitfee</t>
         </is>
       </c>
       <c r="D12" s="5" t="n"/>
@@ -2667,7 +2667,7 @@
       <c r="I12" s="6" t="n"/>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>2039610320817</t>
+          <t>2047560571760</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -2676,25 +2676,25 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>405</v>
+        <v>350</v>
       </c>
       <c r="M12" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="N12" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="O12" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="N12" s="4" t="n">
-        <v>30</v>
-      </c>
-      <c r="O12" s="4" t="n">
-        <v>230</v>
-      </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/1.webp</t>
+          <t>https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/1.webp</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/13.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/14.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/15.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/16.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/17.webp</t>
+          <t>https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/2.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/3.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/4.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/5.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/6.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/7.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/8.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171648/images/big/9.webp</t>
         </is>
       </c>
       <c r="R12" s="4" t="n"/>
@@ -2705,22 +2705,22 @@
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>JMSolution</t>
+          <t>Petitfee</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Disney</t>
+          <t>PETITFEE - MASK 5</t>
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W12" s="4" t="n"/>
       <c r="X12" s="4" t="n"/>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>Water; Methylpropanediol; Glycerin; Glycereth-26; PEG/PPG-17/6 Copolymer; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Hyaluronic Acid; Collagen Extract; Allantoin; Trehalose; Betaine; Ethylhexylglycerin; Xanthan Gum; Hydroxyethylcellulose; Dipropylene Glycol; Butylene Glycol; Disodium Phosphate; Pentylene Glycol; Sodium Phosphate; Disodium EDTA; Glycine; Serine; Glutamic Acid; Aspartic Acid; Leucine; Alanine; Lysine; Proline; Threonine; Valine; 1,2-Hexanediol; PEG-60 Hydrogenated Castor Oil; Rosa Damascena Flower Water; Rosa Damascena Flower Oil; Phenoxyethanol</t>
+          <t>Water;Glycerin;Calcium Chloride;Methylpropanediol;Ceratonia Siliqua (Carob) Gum;Xanthan Gum;Ethyl Hexanediol;PEG-60 Hydrogenated Castor Oil;Chondrus Crispus Powder;Phenoxyethanol;Scutellaria Baicalensis Root Extract;Camellia Sinensis Leaf Extract;Hexanediol;Caprylyl Glycol;Chlorphenesin;Citrus Junos Fruit Extract;Tagetes Erecta Flower Extract;Lavandula Angustifolia (Lavender) Extract;Monarda Didyma Leaf Extract;Mentha Piperita (Peppermint) Leaf Extract</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
@@ -2732,32 +2732,30 @@
       <c r="AB12" s="4" t="n"/>
       <c r="AC12" s="4" t="inlineStr">
         <is>
-          <t>GP Club Co., Ltd.</t>
+          <t>Barunson Co., Ltd.</t>
         </is>
       </c>
       <c r="AD12" s="4" t="n"/>
       <c r="AE12" s="4" t="n"/>
       <c r="AF12" s="4" t="inlineStr">
         <is>
-          <t>Набор тканевых масок для лица JMsolution Mask подходят для быстрого ежедневного ухода за кожей.
-Маска для лица выравнивает тон, устраняет тусклость и следы усталости, придаёт коже естественное сияние и отлично увлажняет. Яркий дизайн упаковки с любимыми персонажами Disney делает набор отличным подарком. Содержит гидролат лимона, витамины C, E и B12, а также бета-глюкан, комплекс аминокислот и пробиотики.</t>
+          <t xml:space="preserve">Гидрогелевая маска для лица – это мощное средство против сухости и усталости кожи! Организуйте эффективный уход за кожей лица с известным корейским брендом PETITFEE.
+В корейских набор масок для лица входят все 7 масок базовой коллекции Petitfee Hydrogel Face Mask: охлаждающую маску с агавой, тонизирующую с какао и кофеином, маску от отеков на лице с артишоком, осветляющую с ромашкой и витамином C, золотую серию Petitifee с безупречным действием от морщин на лице - антивозрастные маски с золотом, черным жемчугом и муцином улитки!
+Маски для лица PETITIFEE уже с первого применения вернут лицу свежий, отдохнувший вид, успокоят кожу и напитают ценными природными экстрактами. Такой набор косметики для женщин станет универсальным подарком, так как увлажняющая маска для лица – это незаменимый продукт в уходе для любой женщины! Независимо от типа кожи и возраста, увлажнение всегда необходимо по утрам и вечерам, поэтому гидрогелевые маски для лица подойдут всем.
+Каждая гидрогелевая маска для лица состоит из двух частей, которые нужно разместить на лице: одну над другой. Мягкая гелевая основа аккуратно прилегает к лицу, повторяя его контуры: это эффективно от морщин на лице и сухости отдельных труднодоступных участков. Такой уход за лицом в некоторых аспектах полезнее, чем обычная масочка тканевая! Косметологи рекомендуют чередовать маски косметические на тканевой и гидрогелевой основе, чтобы достичь максимального эффекта в домашнем уходе. </t>
         </is>
       </c>
       <c r="AG12" s="4" t="n"/>
       <c r="AH12" s="4" t="n"/>
       <c r="AI12" s="4" t="inlineStr">
         <is>
-          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
-        </is>
-      </c>
-      <c r="AJ12" s="4" t="inlineStr">
-        <is>
-          <t>Гиалуроновая кислота;Коллаген</t>
-        </is>
-      </c>
+          <t>На очищенную кожу лица наложите гидрогелевую маску (верхнюю и нижнюю части), плотно прижмите и оставьте на 20–30 минут. Снимите маску и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно. Используйте 2–3 раза в неделю.</t>
+        </is>
+      </c>
+      <c r="AJ12" s="4" t="n"/>
       <c r="AK12" s="4" t="inlineStr">
         <is>
-          <t>Тканевая</t>
+          <t>Гидрогелевая</t>
         </is>
       </c>
       <c r="AL12" s="4" t="inlineStr">
@@ -2767,7 +2765,7 @@
       </c>
       <c r="AM12" s="4" t="inlineStr">
         <is>
-          <t>Увлажнение;Питание</t>
+          <t>Увлажнение;Восстановление</t>
         </is>
       </c>
       <c r="AN12" s="4" t="inlineStr">
@@ -2818,12 +2816,12 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black</t>
+          <t>PETITFEE - MASK 6</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Маски для лица тканевые JMSolution</t>
+          <t>Гидрогелевые маски для лица набор 6 шт. Petitfee</t>
         </is>
       </c>
       <c r="D13" s="5" t="n"/>
@@ -2842,36 +2840,32 @@
         </is>
       </c>
       <c r="I13" s="6" t="n"/>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>2039610565850</t>
-        </is>
-      </c>
+      <c r="J13" s="4" t="n"/>
       <c r="K13" s="4" t="inlineStr">
         <is>
           <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/1.webp</t>
+          <t>https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/1.webp</t>
         </is>
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/13.webp</t>
+          <t>https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/2.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/3.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/4.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/5.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/6.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/7.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/8.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/9.webp;https://basket-32.wbbasket.ru/vol6641/part664171/664171647/images/big/10.webp</t>
         </is>
       </c>
       <c r="R13" s="4" t="n"/>
@@ -2882,22 +2876,22 @@
       </c>
       <c r="T13" s="4" t="inlineStr">
         <is>
-          <t>JMSolution</t>
+          <t>Petitfee</t>
         </is>
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
-          <t>JMSOLUTION - Mask Pack Black</t>
+          <t>PETITFEE - MASK 6</t>
         </is>
       </c>
       <c r="V13" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W13" s="4" t="n"/>
       <c r="X13" s="4" t="n"/>
       <c r="Y13" s="4" t="inlineStr">
         <is>
-          <t>Water; Glycerin; Dipropylene Glycol; Sea Water; Butylene Glycol; 1,2-Hexanediol; Hydrolyzed Collagen; Hydrolyzed Conchiolin Protein; Pearl Extract; Undaria Pinnatifida Extract; Codium Fragile Extract; Enteromorpha Compressa Extract; Laminaria Japonica Extract; Salicornia Herbacea Extract; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Sodium Acetylated Hyaluronate; Olive Oil; Tocopheryl Acetate; Polysorbate 20; Ethylhexylglycerin; Carbomer; Tromethamine; Disodium EDTA; Phenoxyethanol; Fragrance</t>
+          <t>Water;Glycerin;Calcium Chloride;Methylpropanediol;Ceratonia Siliqua (Carob) Gum;Xanthan Gum;Ethyl Hexanediol;PEG-60 Hydrogenated Castor Oil;Chondrus Crispus Powder;Phenoxyethanol;Scutellaria Baicalensis Root Extract;Camellia Sinensis Leaf Extract;Hexanediol;Caprylyl Glycol;Chlorphenesin;Citrus Junos Fruit Extract;Tagetes Erecta Flower Extract;Lavandula Angustifolia (Lavender) Extract;Monarda Didyma Leaf Extract;Mentha Piperita (Peppermint) Leaf Extract</t>
         </is>
       </c>
       <c r="Z13" s="4" t="inlineStr">
@@ -2909,32 +2903,30 @@
       <c r="AB13" s="4" t="n"/>
       <c r="AC13" s="4" t="inlineStr">
         <is>
-          <t>GP Club Co., Ltd.</t>
+          <t>Barunson Co., Ltd.</t>
         </is>
       </c>
       <c r="AD13" s="4" t="n"/>
       <c r="AE13" s="4" t="n"/>
       <c r="AF13" s="4" t="inlineStr">
         <is>
-          <t>Маски для лица тканевые от корейского бренда JMsolution — настоящий экспресс-уход за кожей. Эффективные и универсальные составы, которые подойдут каждой девушке. Благодаря ультратонкой основе, проработанному лекалу и большому количеству эссенции, маска тканевая для лица всего за 20 минут интенсивно насыщает кожу влагой, помогает снять красноту, придавая коже естественное здоровое сияние.Премиальные подарочные наборы масок представлены из 10 шт в боксе. Маски для лица корейские для интенсивного ухода за кожей лица позволит познакомиться с разными масками бренда. Маски выравнивают цвет лица, тон и рельеф кожи, снимает отеки, разглаживает морщины, а также осветляет пигментацию и оказывает лифтинг - эффект. Набор масок тканевых подойдет любому типу кожи: тусклой, нормальной, проблемной, увядающей и антивозрастной. Маска увлажняющая, отбеливающая, восстанавливающая, питающая. Она убирает сухость и шелушение, делает кожу более нежной, гладкой, сияющей. Благодаря ей, кожа становится светлее, очищается и становится более подтянутой. Влажные тканевые маски для лица набор – это и омолаживающий эффект. Успокаивающая маска эффективно борется с проблемами кожи, снимает напряжение и усталость, раздражения и воспаления, устраняет отёки.
-Особым спросом у девушек и женщин пользуются ассорти масок, разных составов в подарочной коробке. Косметические маски в боксе популярны как подарочный набор уходовой косметики.</t>
+          <t xml:space="preserve">Гидрогелевая маска для лица – это мощное средство против сухости и усталости кожи! Организуйте эффективный уход за кожей лица с известным корейским брендом PETITFEE.
+В корейских набор масок для лица входят все 7 масок базовой коллекции Petitfee Hydrogel Face Mask: охлаждающую маску с агавой, тонизирующую с какао и кофеином, маску от отеков на лице с артишоком, осветляющую с ромашкой и витамином C, золотую серию Petitifee с безупречным действием от морщин на лице - антивозрастные маски с золотом, черным жемчугом и муцином улитки!
+Маски для лица PETITIFEE уже с первого применения вернут лицу свежий, отдохнувший вид, успокоят кожу и напитают ценными природными экстрактами. Такой набор косметики для женщин станет универсальным подарком, так как увлажняющая маска для лица – это незаменимый продукт в уходе для любой женщины! Независимо от типа кожи и возраста, увлажнение всегда необходимо по утрам и вечерам, поэтому гидрогелевые маски для лица подойдут всем.
+Каждая гидрогелевая маска для лица состоит из двух частей, которые нужно разместить на лице: одну над другой. Мягкая гелевая основа аккуратно прилегает к лицу, повторяя его контуры: это эффективно от морщин на лице и сухости отдельных труднодоступных участков. Такой уход за лицом в некоторых аспектах полезнее, чем обычная масочка тканевая! Косметологи рекомендуют чередовать маски косметические на тканевой и гидрогелевой основе, чтобы достичь максимального эффекта в домашнем уходе. </t>
         </is>
       </c>
       <c r="AG13" s="4" t="n"/>
       <c r="AH13" s="4" t="n"/>
       <c r="AI13" s="4" t="inlineStr">
         <is>
-          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
-        </is>
-      </c>
-      <c r="AJ13" s="4" t="inlineStr">
-        <is>
-          <t>Коллаген;Гиалуроновая кислота</t>
-        </is>
-      </c>
+          <t>На очищенную кожу лица наложите гидрогелевую маску (верхнюю и нижнюю части), плотно прижмите и оставьте на 20–30 минут. Снимите маску и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно. Используйте 2–3 раза в неделю.</t>
+        </is>
+      </c>
+      <c r="AJ13" s="4" t="n"/>
       <c r="AK13" s="4" t="inlineStr">
         <is>
-          <t>Тканевая</t>
+          <t>Гидрогелевая</t>
         </is>
       </c>
       <c r="AL13" s="4" t="inlineStr">
@@ -2944,7 +2936,7 @@
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>Увлажнение</t>
+          <t>Увлажнение;Восстановление</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
@@ -2995,12 +2987,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>PETITFEE - MASK 7</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Увлажняющие тканевые маски для лица Корея 15 штук Jigott</t>
+          <t>Гидрогелевые маски для лица набор 7 шт. Petitfee</t>
         </is>
       </c>
       <c r="D14" s="5" t="n"/>
@@ -3021,7 +3013,7 @@
       <c r="I14" s="6" t="n"/>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>2041007880460</t>
+          <t>2041007883638</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
@@ -3030,25 +3022,25 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>474</v>
+        <v>350</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/1.webp</t>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/1.webp</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/2.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/3.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/4.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/5.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/6.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/7.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/8.webp</t>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/2.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/3.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/4.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/5.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/6.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574854/images/big/7.webp</t>
         </is>
       </c>
       <c r="R14" s="4" t="n"/>
@@ -3059,22 +3051,22 @@
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>Jigott</t>
+          <t>Petitfee</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>JIGOTT - MASK 15</t>
+          <t>PETITFEE - MASK 7</t>
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="W14" s="4" t="n"/>
       <c r="X14" s="4" t="n"/>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>Water; Glycerin; Butylene Glycol; Betaine; Carbomer; Triethanolamine; Disodium EDTA; Hydroxyethylcellulose; Polysorbate 20; Sodium Hyaluronate; Tocopheryl Acetate; Allantoin; Panthenol; Portulaca Oleracea Extract; 1,2-Hexanediol; Phenoxyethanol; Fragrance</t>
+          <t>Water;Glycerin;Calcium Chloride;Methylpropanediol;Ceratonia Siliqua (Carob) Gum;Xanthan Gum;Ethyl Hexanediol;PEG-60 Hydrogenated Castor Oil;Chondrus Crispus Powder;Phenoxyethanol;Scutellaria Baicalensis Root Extract;Camellia Sinensis Leaf Extract;Hexanediol;Caprylyl Glycol;Chlorphenesin;Citrus Junos Fruit Extract;Tagetes Erecta Flower Extract;Lavandula Angustifolia (Lavender) Extract;Monarda Didyma Leaf Extract;Mentha Piperita (Peppermint) Leaf Extract</t>
         </is>
       </c>
       <c r="Z14" s="4" t="inlineStr">
@@ -3086,12 +3078,541 @@
       <c r="AB14" s="4" t="n"/>
       <c r="AC14" s="4" t="inlineStr">
         <is>
-          <t>Skinine Cosmetic Co., Ltd.</t>
+          <t>Barunson Co., Ltd.</t>
         </is>
       </c>
       <c r="AD14" s="4" t="n"/>
       <c r="AE14" s="4" t="n"/>
       <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Гидрогелевая маска для лица – это мощное средство против сухости и усталости кожи! Организуйте эффективный уход за кожей лица с известным корейским брендом PETITFEE.
+В корейских набор масок для лица входят все 7 масок базовой коллекции Petitfee Hydrogel Face Mask: охлаждающую маску с агавой, тонизирующую с какао и кофеином, маску от отеков на лице с артишоком, осветляющую с ромашкой и витамином C, золотую серию Petitifee с безупречным действием от морщин на лице - антивозрастные маски с золотом, черным жемчугом и муцином улитки!
+Маски для лица PETITIFEE уже с первого применения вернут лицу свежий, отдохнувший вид, успокоят кожу и напитают ценными природными экстрактами. Такой набор косметики для женщин станет универсальным подарком, так как увлажняющая маска для лица – это незаменимый продукт в уходе для любой женщины! Независимо от типа кожи и возраста, увлажнение всегда необходимо по утрам и вечерам, поэтому гидрогелевые маски для лица подойдут всем.
+Каждая гидрогелевая маска для лица состоит из двух частей, которые нужно разместить на лице: одну над другой. Мягкая гелевая основа аккуратно прилегает к лицу, повторяя его контуры: это эффективно от морщин на лице и сухости отдельных труднодоступных участков. Такой уход за лицом в некоторых аспектах полезнее, чем обычная масочка тканевая! Косметологи рекомендуют чередовать маски косметические на тканевой и гидрогелевой основе, чтобы достичь максимального эффекта в домашнем уходе. </t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="n"/>
+      <c r="AH14" s="4" t="n"/>
+      <c r="AI14" s="4" t="inlineStr">
+        <is>
+          <t>На очищенную кожу лица наложите гидрогелевую маску (верхнюю и нижнюю части), плотно прижмите и оставьте на 20–30 минут. Снимите маску и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно. Используйте 2–3 раза в неделю.</t>
+        </is>
+      </c>
+      <c r="AJ14" s="4" t="n"/>
+      <c r="AK14" s="4" t="inlineStr">
+        <is>
+          <t>Гидрогелевая</t>
+        </is>
+      </c>
+      <c r="AL14" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM14" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение;Восстановление</t>
+        </is>
+      </c>
+      <c r="AN14" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO14" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
+      <c r="AP14" s="4" t="n"/>
+      <c r="AQ14" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR14" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS14" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
+      <c r="AT14" s="4" t="n"/>
+      <c r="AU14" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW14" s="4" t="n"/>
+      <c r="AX14" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AY14" s="4" t="n"/>
+      <c r="AZ14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Disney</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Набор корейских тканевых масок для лица 10 шт JMSolution</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2039610320817</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>405</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>180</v>
+      </c>
+      <c r="N15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>230</v>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/13.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/14.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/15.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/16.webp;https://basket-14.wbbasket.ru/vol2149/part214964/214964091/images/big/17.webp</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>JMSolution</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Disney</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W15" s="4" t="n"/>
+      <c r="X15" s="4" t="n"/>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>Water; Methylpropanediol; Glycerin; Glycereth-26; PEG/PPG-17/6 Copolymer; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Hyaluronic Acid; Collagen Extract; Allantoin; Trehalose; Betaine; Ethylhexylglycerin; Xanthan Gum; Hydroxyethylcellulose; Dipropylene Glycol; Butylene Glycol; Disodium Phosphate; Pentylene Glycol; Sodium Phosphate; Disodium EDTA; Glycine; Serine; Glutamic Acid; Aspartic Acid; Leucine; Alanine; Lysine; Proline; Threonine; Valine; 1,2-Hexanediol; PEG-60 Hydrogenated Castor Oil; Rosa Damascena Flower Water; Rosa Damascena Flower Oil; Phenoxyethanol</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="n"/>
+      <c r="AB15" s="4" t="n"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>GP Club Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="n"/>
+      <c r="AE15" s="4" t="n"/>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>Набор тканевых масок для лица JMsolution Mask подходят для быстрого ежедневного ухода за кожей.
+Маска для лица выравнивает тон, устраняет тусклость и следы усталости, придаёт коже естественное сияние и отлично увлажняет. Яркий дизайн упаковки с любимыми персонажами Disney делает набор отличным подарком. Содержит гидролат лимона, витамины C, E и B12, а также бета-глюкан, комплекс аминокислот и пробиотики.</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="n"/>
+      <c r="AH15" s="4" t="n"/>
+      <c r="AI15" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ15" s="4" t="inlineStr">
+        <is>
+          <t>Гиалуроновая кислота;Коллаген</t>
+        </is>
+      </c>
+      <c r="AK15" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL15" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM15" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение;Питание</t>
+        </is>
+      </c>
+      <c r="AN15" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO15" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
+      <c r="AP15" s="4" t="n"/>
+      <c r="AQ15" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR15" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS15" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
+      <c r="AT15" s="4" t="n"/>
+      <c r="AU15" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW15" s="4" t="n"/>
+      <c r="AX15" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AY15" s="4" t="n"/>
+      <c r="AZ15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Маски для лица тканевые JMSolution</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2039610565850</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>300</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>190</v>
+      </c>
+      <c r="N16" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/2.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/3.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/4.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/5.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/6.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/7.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/8.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/9.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/10.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/11.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/12.webp;https://basket-14.wbbasket.ru/vol2149/part214977/214977901/images/big/13.webp</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>JMSolution</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>JMSOLUTION - Mask Pack Black</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" s="4" t="n"/>
+      <c r="X16" s="4" t="n"/>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycerin; Dipropylene Glycol; Sea Water; Butylene Glycol; 1,2-Hexanediol; Hydrolyzed Collagen; Hydrolyzed Conchiolin Protein; Pearl Extract; Undaria Pinnatifida Extract; Codium Fragile Extract; Enteromorpha Compressa Extract; Laminaria Japonica Extract; Salicornia Herbacea Extract; Sodium Hyaluronate; Hydrolyzed Hyaluronic Acid; Sodium Acetylated Hyaluronate; Olive Oil; Tocopheryl Acetate; Polysorbate 20; Ethylhexylglycerin; Carbomer; Tromethamine; Disodium EDTA; Phenoxyethanol; Fragrance</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="n"/>
+      <c r="AB16" s="4" t="n"/>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>GP Club Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="n"/>
+      <c r="AE16" s="4" t="n"/>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>Маски для лица тканевые от корейского бренда JMsolution — настоящий экспресс-уход за кожей. Эффективные и универсальные составы, которые подойдут каждой девушке. Благодаря ультратонкой основе, проработанному лекалу и большому количеству эссенции, маска тканевая для лица всего за 20 минут интенсивно насыщает кожу влагой, помогает снять красноту, придавая коже естественное здоровое сияние.Премиальные подарочные наборы масок представлены из 10 шт в боксе. Маски для лица корейские для интенсивного ухода за кожей лица позволит познакомиться с разными масками бренда. Маски выравнивают цвет лица, тон и рельеф кожи, снимает отеки, разглаживает морщины, а также осветляет пигментацию и оказывает лифтинг - эффект. Набор масок тканевых подойдет любому типу кожи: тусклой, нормальной, проблемной, увядающей и антивозрастной. Маска увлажняющая, отбеливающая, восстанавливающая, питающая. Она убирает сухость и шелушение, делает кожу более нежной, гладкой, сияющей. Благодаря ей, кожа становится светлее, очищается и становится более подтянутой. Влажные тканевые маски для лица набор – это и омолаживающий эффект. Успокаивающая маска эффективно борется с проблемами кожи, снимает напряжение и усталость, раздражения и воспаления, устраняет отёки.
+Особым спросом у девушек и женщин пользуются ассорти масок, разных составов в подарочной коробке. Косметические маски в боксе популярны как подарочный набор уходовой косметики.</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="n"/>
+      <c r="AH16" s="4" t="n"/>
+      <c r="AI16" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ16" s="4" t="inlineStr">
+        <is>
+          <t>Коллаген;Гиалуроновая кислота</t>
+        </is>
+      </c>
+      <c r="AK16" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL16" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM16" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение</t>
+        </is>
+      </c>
+      <c r="AN16" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO16" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
+      <c r="AP16" s="4" t="n"/>
+      <c r="AQ16" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR16" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS16" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
+      <c r="AT16" s="4" t="n"/>
+      <c r="AU16" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV16" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW16" s="4" t="n"/>
+      <c r="AX16" s="4" t="n">
+        <v>1095</v>
+      </c>
+      <c r="AY16" s="4" t="n"/>
+      <c r="AZ16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - MASK 15</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Увлажняющие тканевые маски для лица Корея 15 штук Jigott</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2041007880460</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>3304990000 - Прочие косметические средства или средства для макияжа и средства для ухода за кожей (кроме лекарственных), включая средства против загара или для загара; средства для маникюра или педикюра</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>474</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>140</v>
+      </c>
+      <c r="N17" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/1.webp</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/2.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/3.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/4.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/5.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/6.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/7.webp;https://basket-16.wbbasket.ru/vol2555/part255574/255574453/images/big/8.webp</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>Маска косметическая</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>Jigott</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>JIGOTT - MASK 15</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="W17" s="4" t="n"/>
+      <c r="X17" s="4" t="n"/>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>Water; Glycerin; Butylene Glycol; Betaine; Carbomer; Triethanolamine; Disodium EDTA; Hydroxyethylcellulose; Polysorbate 20; Sodium Hyaluronate; Tocopheryl Acetate; Allantoin; Panthenol; Portulaca Oleracea Extract; 1,2-Hexanediol; Phenoxyethanol; Fragrance</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="n"/>
+      <c r="AB17" s="4" t="n"/>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>Skinine Cosmetic Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="n"/>
+      <c r="AE17" s="4" t="n"/>
+      <c r="AF17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Набор увлажняющих масок для лица включает 15 разных масочек тканевых от бренда JIGOTT. Маски не повторяются! 
 В набор косметических корейских масок для лица входят JIGOTT:
@@ -3114,234 +3635,72 @@
 Тканевую косметическую маску Джиготт можно использовать в любое время дня на очищенное лицо. </t>
         </is>
       </c>
-      <c r="AG14" s="4" t="n"/>
-      <c r="AH14" s="4" t="n"/>
-      <c r="AI14" s="4" t="inlineStr">
-        <is>
-          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
-        </is>
-      </c>
-      <c r="AJ14" s="4" t="inlineStr">
-        <is>
-          <t>Гиалуроновая кислота</t>
-        </is>
-      </c>
-      <c r="AK14" s="4" t="inlineStr">
-        <is>
-          <t>Тканевая</t>
-        </is>
-      </c>
-      <c r="AL14" s="4" t="inlineStr">
-        <is>
-          <t>Для всех типов кожи</t>
-        </is>
-      </c>
-      <c r="AM14" s="4" t="inlineStr">
-        <is>
-          <t>Увлажнение</t>
-        </is>
-      </c>
-      <c r="AN14" s="4" t="inlineStr">
-        <is>
-          <t>Дневной уход;Ночной уход</t>
-        </is>
-      </c>
-      <c r="AO14" s="4" t="inlineStr">
-        <is>
-          <t>Лицо</t>
-        </is>
-      </c>
-      <c r="AP14" s="4" t="n"/>
-      <c r="AQ14" s="4" t="inlineStr">
-        <is>
-          <t>Взрослая</t>
-        </is>
-      </c>
-      <c r="AR14" s="4" t="inlineStr">
-        <is>
-          <t>Женский</t>
-        </is>
-      </c>
-      <c r="AS14" s="4" t="inlineStr">
-        <is>
-          <t>Для любого возраста</t>
-        </is>
-      </c>
-      <c r="AT14" s="4" t="n"/>
-      <c r="AU14" s="4" t="inlineStr">
-        <is>
-          <t>Южная Корея</t>
-        </is>
-      </c>
-      <c r="AV14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW14" s="4" t="n"/>
-      <c r="AX14" s="4" t="n">
-        <v>1095</v>
-      </c>
-      <c r="AY14" s="4" t="n"/>
-      <c r="AZ14" s="4" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="6" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-      <c r="P15" s="4" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
-      <c r="T15" s="4" t="n"/>
-      <c r="U15" s="4" t="n"/>
-      <c r="V15" s="4" t="n"/>
-      <c r="W15" s="4" t="n"/>
-      <c r="X15" s="4" t="n"/>
-      <c r="Y15" s="4" t="n"/>
-      <c r="Z15" s="4" t="n"/>
-      <c r="AA15" s="4" t="n"/>
-      <c r="AB15" s="4" t="n"/>
-      <c r="AC15" s="4" t="n"/>
-      <c r="AD15" s="4" t="n"/>
-      <c r="AE15" s="4" t="n"/>
-      <c r="AF15" s="4" t="n"/>
-      <c r="AG15" s="4" t="n"/>
-      <c r="AH15" s="4" t="n"/>
-      <c r="AI15" s="4" t="n"/>
-      <c r="AJ15" s="4" t="n"/>
-      <c r="AK15" s="4" t="n"/>
-      <c r="AL15" s="4" t="n"/>
-      <c r="AM15" s="4" t="n"/>
-      <c r="AN15" s="4" t="n"/>
-      <c r="AO15" s="4" t="n"/>
-      <c r="AP15" s="4" t="n"/>
-      <c r="AQ15" s="4" t="n"/>
-      <c r="AR15" s="4" t="n"/>
-      <c r="AS15" s="4" t="n"/>
-      <c r="AT15" s="4" t="n"/>
-      <c r="AU15" s="4" t="n"/>
-      <c r="AV15" s="4" t="n"/>
-      <c r="AW15" s="4" t="n"/>
-      <c r="AX15" s="4" t="n"/>
-      <c r="AY15" s="4" t="n"/>
-      <c r="AZ15" s="4" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="6" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
-      <c r="P16" s="4" t="n"/>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
-      <c r="T16" s="4" t="n"/>
-      <c r="U16" s="4" t="n"/>
-      <c r="V16" s="4" t="n"/>
-      <c r="W16" s="4" t="n"/>
-      <c r="X16" s="4" t="n"/>
-      <c r="Y16" s="4" t="n"/>
-      <c r="Z16" s="4" t="n"/>
-      <c r="AA16" s="4" t="n"/>
-      <c r="AB16" s="4" t="n"/>
-      <c r="AC16" s="4" t="n"/>
-      <c r="AD16" s="4" t="n"/>
-      <c r="AE16" s="4" t="n"/>
-      <c r="AF16" s="4" t="n"/>
-      <c r="AG16" s="4" t="n"/>
-      <c r="AH16" s="4" t="n"/>
-      <c r="AI16" s="4" t="n"/>
-      <c r="AJ16" s="4" t="n"/>
-      <c r="AK16" s="4" t="n"/>
-      <c r="AL16" s="4" t="n"/>
-      <c r="AM16" s="4" t="n"/>
-      <c r="AN16" s="4" t="n"/>
-      <c r="AO16" s="4" t="n"/>
-      <c r="AP16" s="4" t="n"/>
-      <c r="AQ16" s="4" t="n"/>
-      <c r="AR16" s="4" t="n"/>
-      <c r="AS16" s="4" t="n"/>
-      <c r="AT16" s="4" t="n"/>
-      <c r="AU16" s="4" t="n"/>
-      <c r="AV16" s="4" t="n"/>
-      <c r="AW16" s="4" t="n"/>
-      <c r="AX16" s="4" t="n"/>
-      <c r="AY16" s="4" t="n"/>
-      <c r="AZ16" s="4" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
-      <c r="N17" s="4" t="n"/>
-      <c r="O17" s="4" t="n"/>
-      <c r="P17" s="4" t="n"/>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
-      <c r="T17" s="4" t="n"/>
-      <c r="U17" s="4" t="n"/>
-      <c r="V17" s="4" t="n"/>
-      <c r="W17" s="4" t="n"/>
-      <c r="X17" s="4" t="n"/>
-      <c r="Y17" s="4" t="n"/>
-      <c r="Z17" s="4" t="n"/>
-      <c r="AA17" s="4" t="n"/>
-      <c r="AB17" s="4" t="n"/>
-      <c r="AC17" s="4" t="n"/>
-      <c r="AD17" s="4" t="n"/>
-      <c r="AE17" s="4" t="n"/>
-      <c r="AF17" s="4" t="n"/>
       <c r="AG17" s="4" t="n"/>
       <c r="AH17" s="4" t="n"/>
-      <c r="AI17" s="4" t="n"/>
-      <c r="AJ17" s="4" t="n"/>
-      <c r="AK17" s="4" t="n"/>
-      <c r="AL17" s="4" t="n"/>
-      <c r="AM17" s="4" t="n"/>
-      <c r="AN17" s="4" t="n"/>
-      <c r="AO17" s="4" t="n"/>
+      <c r="AI17" s="4" t="inlineStr">
+        <is>
+          <t>После очищения и тонизирования достаньте маску, разверните и наложите на лицо, совместив вырезы для глаз, носа и губ. Разгладьте и оставьте на 15–20 минут, затем снимите и мягко вбейте остатки эссенции подушечками пальцев до впитывания; смывать не нужно.</t>
+        </is>
+      </c>
+      <c r="AJ17" s="4" t="inlineStr">
+        <is>
+          <t>Гиалуроновая кислота</t>
+        </is>
+      </c>
+      <c r="AK17" s="4" t="inlineStr">
+        <is>
+          <t>Тканевая</t>
+        </is>
+      </c>
+      <c r="AL17" s="4" t="inlineStr">
+        <is>
+          <t>Для всех типов кожи</t>
+        </is>
+      </c>
+      <c r="AM17" s="4" t="inlineStr">
+        <is>
+          <t>Увлажнение</t>
+        </is>
+      </c>
+      <c r="AN17" s="4" t="inlineStr">
+        <is>
+          <t>Дневной уход;Ночной уход</t>
+        </is>
+      </c>
+      <c r="AO17" s="4" t="inlineStr">
+        <is>
+          <t>Лицо</t>
+        </is>
+      </c>
       <c r="AP17" s="4" t="n"/>
-      <c r="AQ17" s="4" t="n"/>
-      <c r="AR17" s="4" t="n"/>
-      <c r="AS17" s="4" t="n"/>
+      <c r="AQ17" s="4" t="inlineStr">
+        <is>
+          <t>Взрослая</t>
+        </is>
+      </c>
+      <c r="AR17" s="4" t="inlineStr">
+        <is>
+          <t>Женский</t>
+        </is>
+      </c>
+      <c r="AS17" s="4" t="inlineStr">
+        <is>
+          <t>Для любого возраста</t>
+        </is>
+      </c>
       <c r="AT17" s="4" t="n"/>
-      <c r="AU17" s="4" t="n"/>
-      <c r="AV17" s="4" t="n"/>
+      <c r="AU17" s="4" t="inlineStr">
+        <is>
+          <t>Южная Корея</t>
+        </is>
+      </c>
+      <c r="AV17" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="AW17" s="4" t="n"/>
-      <c r="AX17" s="4" t="n"/>
+      <c r="AX17" s="4" t="n">
+        <v>1095</v>
+      </c>
       <c r="AY17" s="4" t="n"/>
       <c r="AZ17" s="4" t="n"/>
     </row>
